--- a/Section V Results and Discussion/Training-2/ReviewersdataRankingv7.xlsx
+++ b/Section V Results and Discussion/Training-2/ReviewersdataRankingv7.xlsx
@@ -96,7 +96,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,6 +115,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -597,137 +604,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -739,6 +746,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1147,11 +1155,11 @@
       <c r="E2" s="4">
         <v>95.8272</v>
       </c>
-      <c r="F2" s="4">
-        <v>0.1797</v>
-      </c>
-      <c r="G2" s="4">
-        <v>17.2201</v>
+      <c r="F2" s="5">
+        <v>0.6485</v>
+      </c>
+      <c r="G2" s="5">
+        <v>62.144</v>
       </c>
       <c r="H2" s="4">
         <v>0.989110589685106</v>
@@ -1185,11 +1193,11 @@
       <c r="E3" s="4">
         <v>52.6473</v>
       </c>
-      <c r="F3" s="4">
-        <v>0.2011</v>
-      </c>
-      <c r="G3" s="4">
-        <v>10.5873</v>
+      <c r="F3" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="G3" s="5">
+        <v>35.274</v>
       </c>
       <c r="H3" s="4">
         <v>0.93305</v>
@@ -1223,11 +1231,11 @@
       <c r="E4" s="4">
         <v>30.6127</v>
       </c>
-      <c r="F4" s="4">
-        <v>0.193</v>
-      </c>
-      <c r="G4" s="4">
-        <v>5.9082</v>
+      <c r="F4" s="5">
+        <v>0.6682</v>
+      </c>
+      <c r="G4" s="5">
+        <v>20.455</v>
       </c>
       <c r="H4" s="4">
         <v>0.893478611847671</v>
@@ -1261,11 +1269,11 @@
       <c r="E5" s="4">
         <v>27.2996</v>
       </c>
-      <c r="F5" s="4">
-        <v>0.2104</v>
-      </c>
-      <c r="G5" s="4">
-        <v>5.7438</v>
+      <c r="F5" s="5">
+        <v>0.679</v>
+      </c>
+      <c r="G5" s="5">
+        <v>18.536</v>
       </c>
       <c r="H5" s="4">
         <v>0.64058</v>
@@ -1299,11 +1307,11 @@
       <c r="E6" s="4">
         <v>5.4215</v>
       </c>
-      <c r="F6" s="4">
-        <v>0.1843</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0.9991</v>
+      <c r="F6" s="5">
+        <v>0.6717</v>
+      </c>
+      <c r="G6" s="5">
+        <v>3.642</v>
       </c>
       <c r="H6" s="4">
         <v>0.78431075549828</v>
@@ -1337,11 +1345,11 @@
       <c r="E7" s="4">
         <v>20.4435</v>
       </c>
-      <c r="F7" s="4">
-        <v>0.226</v>
-      </c>
-      <c r="G7" s="4">
-        <v>4.6202</v>
+      <c r="F7" s="5">
+        <v>0.6725</v>
+      </c>
+      <c r="G7" s="5">
+        <v>13.748</v>
       </c>
       <c r="H7" s="4">
         <v>0.759984614845855</v>
@@ -1375,11 +1383,11 @@
       <c r="E8" s="4">
         <v>0.9315</v>
       </c>
-      <c r="F8" s="4">
-        <v>0.2058</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0.1917</v>
+      <c r="F8" s="5">
+        <v>0.6618</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.616</v>
       </c>
       <c r="H8" s="4">
         <v>0.899065838647569</v>
